--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:17</t>
+    <t xml:space="preserve">2026-09-09 22:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:16</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,18 +1099,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>13.39</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14.85</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="4">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14.1</v>
+        <v>14.85</v>
       </c>
     </row>
   </sheetData>
@@ -1183,101 +1183,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10.47</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.24</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6.49</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13.39</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>12.52</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12.23</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14.85</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14.36</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13.65</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="11">
@@ -1414,35 +1414,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14.1</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13.64</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13.07</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -797,7 +797,7 @@
         <v>-1.15</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5.83</v>
+        <v>-5.82</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -820,7 +820,7 @@
         <v>-1.46</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-11.03</v>
+        <v>-11.01</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -843,7 +843,7 @@
         <v>-1.29</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-8.06</v>
+        <v>-8.07</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:39</t>
+    <t xml:space="preserve">2026-10-05 07:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
